--- a/artfynd/A 26370-2026 artfynd.xlsx
+++ b/artfynd/A 26370-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65281396</v>
+        <v>65281404</v>
       </c>
       <c r="B2" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592109.8546298681</v>
+        <v>592178</v>
       </c>
       <c r="R2" t="n">
-        <v>6669706.791620382</v>
+        <v>6669677</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,53 +775,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65281347</v>
+        <v>65281390</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1980</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vivastbo, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592051.8016312674</v>
+        <v>592090</v>
       </c>
       <c r="R3" t="n">
-        <v>6669713.801345476</v>
+        <v>6669690</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +856,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65281407</v>
+        <v>65281362</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,36 +886,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vivastbo, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592073.9065203129</v>
+        <v>592024</v>
       </c>
       <c r="R4" t="n">
-        <v>6669668.03219439</v>
+        <v>6669616</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,22 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +957,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65281362</v>
+        <v>65281393</v>
       </c>
       <c r="B5" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,37 +986,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vivastbo, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592023.8220916467</v>
+        <v>592166</v>
       </c>
       <c r="R5" t="n">
-        <v>6669615.966804722</v>
+        <v>6669697</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,22 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,37 +1075,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65281393</v>
+        <v>65281396</v>
       </c>
       <c r="B6" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592165.9759488148</v>
+        <v>592110</v>
       </c>
       <c r="R6" t="n">
-        <v>6669697.243674347</v>
+        <v>6669707</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,37 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65281406</v>
+        <v>65281397</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592125.9840186905</v>
+        <v>591993</v>
       </c>
       <c r="R7" t="n">
-        <v>6669720.147698168</v>
+        <v>6669663</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,19 +1245,9 @@
           <t>2016-09-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,37 +1275,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65281390</v>
+        <v>65281406</v>
       </c>
       <c r="B8" t="n">
-        <v>85176</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1980</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592089.8236386571</v>
+        <v>592126</v>
       </c>
       <c r="R8" t="n">
-        <v>6669689.850793293</v>
+        <v>6669720</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,19 +1345,9 @@
           <t>2016-09-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,37 +1375,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65281397</v>
+        <v>65281407</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591993.2033441258</v>
+        <v>592074</v>
       </c>
       <c r="R9" t="n">
-        <v>6669663.017582827</v>
+        <v>6669668</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1555,19 +1445,9 @@
           <t>2016-09-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-09-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,6 +1472,305 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>65281427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592182</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6669684</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-07-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-07-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>65281377</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592033</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6669583</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-10-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-10-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>65281347</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592052</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6669714</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26370-2026 artfynd.xlsx
+++ b/artfynd/A 26370-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281404</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281390</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281396</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281397</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281406</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281407</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281427</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281377</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,8 +1826,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281347</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>